--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0038.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0038.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Pick Up/Interact</t>
+          <t>Nhặt Lên/Tương Tác</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Công cụ/Quick Access Wheel</t>
+          <t>Bánh xe tiện ích/ truy cập nhanh</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Công cụ/Quick Access Wheel</t>
+          <t>Bánh xe tiện ích/ truy cập nhanh</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 1</t>
+          <t>Đổi sang Thành viên 1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 2</t>
+          <t>Đổi sang Thành viên 2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 3</t>
+          <t>Đổi sang Thành viên 3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 4</t>
+          <t>Chuyển sang Thành viên Đội 4</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 1</t>
+          <t>Đổi sang Thành viên 1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 2</t>
+          <t>Đổi sang Thành viên 2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 3</t>
+          <t>Đổi sang Thành viên 3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Chuyển sang thành viên Đội 4</t>
+          <t>Chuyển sang Thành viên Đội 4</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Navigate</t>
+          <t>Định vị</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Navigate</t>
+          <t>Định vị</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Quit Thử thách</t>
+          <t>Thoát Thử Thách</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Quit Thử thách</t>
+          <t>Thoát Thử Thách</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Thư</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bản đồ</t>
+          <t>Bản Đồ</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Quests</t>
+          <t>Nhiệm vụ</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Túi đồ</t>
+          <t>Hành trang</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Công cụ</t>
+          <t>Tiện ích</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Tutorial</t>
+          <t>Hướng Dẫn</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Show Cursor</t>
+          <t>Hiển thị Con trỏ</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Trò Chuyện</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Sổ tay</t>
+          <t>Sổ Hướng Dẫn</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Triệu Tập</t>
+          <t>Triệu tập</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Podcast Pioneer</t>
+          <t>Podcast Tiên Phong</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Co-op Mode</t>
+          <t>Chế độ Đồng Đội</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Combat và Exploration</t>
+          <t>Chiến Đấu và Thám Hiểm</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Interface</t>
+          <t>Giao diện</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Combat và Exploration</t>
+          <t>Chiến Đấu và Thám Hiểm</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Shortcuts</t>
+          <t>Phím Tắt</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Show Temporary Item First</t>
+          <t>Ưu tiên hiển thị vật phẩm tạm thời</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>New stages unlocked, chạm để tiếp tục</t>
+          <t>Các giai đoạn mới đã mở khóa, chạm để tiếp tục</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>New stages unlocked</t>
+          <t>Các giai đoạn mới đã mở khóa</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Fallacy of Không Return</t>
+          <t>Ảo Tưởng Vô Hồi</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Chat/Refuse</t>
+          <t>Trò chuyện/Từ chối</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>So sánh</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Preview</t>
+          <t>Xem trước</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Tháo tất cả</t>
+          <t>Tháo Tất Cả Trang Bị</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>Cuộn Giấy</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Switch khu vực cuộn</t>
+          <t>Cuộn để chuyển khu vực</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Reward increases with SOL3 Giai đoạn</t>
+          <t>Phần thưởng tăng theo Giai Đoạn SOL3</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Privacy Policy &amp; Setting</t>
+          <t>Chính Sách Bảo Mật &amp; Cài Đặt</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Vui lòng bật quyền truy cập album trong Settings-Ứng dụng để sử dụng tính năng này</t>
+          <t>Vui lòng bật quyền truy cập album trong Cài đặt-Ứng dụng để sử dụng tính năng này</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Vui lòng bật quyền truy cập album trong Settings-Ứng dụng để sử dụng tính năng này</t>
+          <t>Vui lòng bật quyền truy cập album trong Cài đặt-Ứng dụng để sử dụng tính năng này</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Area Effect</t>
+          <t>Hiệu ứng khu vực</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Information at a Glance</t>
+          <t>Thông tin tóm lược</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Echo Info</t>
+          <t>Thông Tin Tiếng Vọng</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Token</t>
+          <t>Mã Đổi</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>OS Notification Feed</t>
+          <t>BẢNG THÔNG BÁO HỆ THỐNG</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Assisted Aiming</t>
+          <t>Hỗ trợ Ngắm Bắn</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Remaining Attempts This Week</t>
+          <t>Lượt còn lại trong tuần</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Rewards</t>
+          <t>Phần thưởng</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Phantom Appearance</t>
+          <t>Hiện Hình Ảo Ảnh</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Reached the Production Limit</t>
+          <t>Đã đạt Giới hạn Sản xuất</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Vai trò chiến đấu</t>
+          <t>Vai Trò Chiến Đấu</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Tips</t>
+          <t>Mẹo</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Tips</t>
+          <t>Mẹo</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi hoàn thành Nhiệm vụ Thám hiểm "Viên Ngọc Trai Của Rồng Huy Hoàng"</t>
+          <t>Mở khóa sau khi hoàn thành Nhiệm Vụ Khám Phá "Viên Ngọc Trai Của Loong Vinh Quang."</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Tips</t>
+          <t>Mẹo</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Resonator not unlocked</t>
+          <t>Resonator chưa được mở khóa</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Lock mục tiêu</t>
+          <t>Khóa mục tiêu</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Mở 1 Rương Cung Ứng</t>
+          <t>Mở 1 Rương Cung Cấp</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Complete 1 Nhiệm Vụ Chính</t>
+          <t>Hoàn thành 1 Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Complete 1 Side Quest</t>
+          <t>Hoàn thành 1 Nhiệm Vụ Phụ</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Complete 1 Exploration Quest</t>
+          <t>Hoàn thành 1 Nhiệm Vụ Thám Hiểm</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Spend 180 Waveplates</t>
+          <t>Tiêu hao 180 Bản Tần Số</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Hoàn thành 1 tầng trong Tower of Adversity</t>
+          <t>Hoàn thành 1 Tầng trong Tháp Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Vượt ải Nightmare Nest hoặc Discord Nest 1 lần</t>
+          <t>Hoàn thành Hang Ác Mộng hoặc Tổ Tacet Discord 1 lần</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Ascension preview</t>
+          <t>Xem Trước Thăng Tiến</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Chọn một tầng</t>
+          <t>Chọn một lớp</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Windchimer Cửa hàng</t>
+          <t>Cửa Hàng Thú Gió</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Emote</t>
+          <t>Biểu cảm</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Quick Reply</t>
+          <t>Trả lời nhanh</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Điều chỉnh Camera Position</t>
+          <t>Điều chỉnh vị trí camera</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Điều chỉnh Angle</t>
+          <t>Điều chỉnh góc quay</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Souvenir Cửa hàng</t>
+          <t>Cửa Hàng Lưu Niệm</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Lễ hội Giấc mơ</t>
+          <t>Lễ Hội Ở Slumberland</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Phantasm Amass</t>
+          <t>Ảo Ảnh Hội Tụ</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Temporal Loop</t>
+          <t>Vòng Lặp Thời Gian</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Lock-on Mode</t>
+          <t>Chế độ Khóa Mục tiêu</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Keyboard &amp; Mouse</t>
+          <t>Bàn Phím &amp; Chuột</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Controller: Invert Horizontal Axis</t>
+          <t>Bộ điều khiển: Đảo chiều Trục ngang</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Controller: Invert Vertical Axis</t>
+          <t>Bộ điều khiển: Đảo chiều Trục dọc</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Bloom</t>
+          <t>Nở Rộ</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>(Giữ) Data Merge</t>
+          <t>(Giữ) Hợp Nhất Dữ Liệu</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Lock-on Priority</t>
+          <t>Ưu tiên Khóa Mục tiêu</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Flight Controls</t>
+          <t>Điều Khiển Bay</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Display UI</t>
+          <t>Hiển thị giao diện</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Chọn Echo</t>
+          <t>Chọn Tiếng Vọng</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Enemy Hit Flash</t>
+          <t>Tia chớp trúng địch</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>(Giữ) Chat</t>
+          <t>(Giữ) Trò chuyện</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>(Giữ) Chat</t>
+          <t>(Giữ) Trò chuyện</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Giữ để dựng gian hàng</t>
+          <t>Giữ để dựng quầy hàng</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>PSN online ID</t>
+          <t>ID trực tuyến PSN</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Move Cursor</t>
+          <t>Di Chuyển Con Trỏ</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Controller Mode</t>
+          <t>Chế Độ Điều Khiển</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Discarded</t>
+          <t>Đã hủy bỏ</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Discard disabled</t>
+          <t>Chức năng hủy bỏ bị vô hiệu hóa</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Discarded</t>
+          <t>Đã hủy bỏ</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Not discarded</t>
+          <t>Chưa bị vứt bỏ</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Zoom in/out</t>
+          <t>Thu phóng</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Auto FPS</t>
+          <t>Tự động FPS</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Chỉnh sửa</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Chơi Co-op chỉ với người dùng PlayStation™Network</t>
+          <t>Chỉ Hợp Tác Với Người Chơi Trên PlayStation™Network</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Controller Vibration Intensity</t>
+          <t>Cường Độ Rung Bộ Điều Khiển</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Controller Vibration Range</t>
+          <t>Phạm Vi Rung Bộ Điều Khiển</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Bộ Điều Khiển</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Di Chuyển</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Modifier Button</t>
+          <t>Nút Bộ Điều Chỉnh</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Modifier Button</t>
+          <t>Nút Bộ Điều Chỉnh</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>This input cannot be remapped</t>
+          <t>Thao tác này không thể gán lại.</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Nhấn nút bạn muốn gán</t>
+          <t>Nhấn nút bạn muốn gán.</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Nút này không hỗ trợ chức năng này</t>
+          <t>Nút này không hỗ trợ chức năng này.</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Edit Quick Access Wheel</t>
+          <t>Chỉnh sửa vòng truy cập nhanh</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Switch Successful</t>
+          <t>Chuyển Thành Công</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Damage Numbers</t>
+          <t>Số Hiệu Sát Thương</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Physics-Based Animation</t>
+          <t>Hoạt Hình Dựa Trên Vật Lý</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Outline</t>
+          <t>Đường Viền</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Biến Đổi: Cuddle Wuddle</t>
+          <t>Biến thân: Ôm Ấm</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Biến Đổi: Lottie Lost</t>
+          <t>Biến thân: Lottie Lạc Lối</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Cutscene Mode</t>
+          <t>Chế độ cắt cảnh</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Immersion Mode</t>
+          <t>Chế độ Hòa Nhập</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Không thể tham gia Co-op khi bị đánh bại</t>
+          <t>Không thể tham gia Hợp Tác khi đã bị đánh bại</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Invert Vertical Axis in Flight</t>
+          <t>Đảo Ngược Trục Dọc Khi Bay</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Invite 1 Companion</t>
+          <t>Mời 1 đồng hành</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Invite 2 Companions</t>
+          <t>Mời 2 đồng hành</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Invite 3 Companions</t>
+          <t>Mời 3 đồng hành</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Invite 4 Companions</t>
+          <t>Mời 4 Cộng Sự</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Invite 5 Companions</t>
+          <t>Mời 5 Cộng Sự</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Invite 6 Companions</t>
+          <t>Mời 6 Cộng Sự</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Invite 7 Companions</t>
+          <t>Mời 7 Cộng Sự</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Squire of the Roving Knight</t>
+          <t>Hộ vệ của Kỵ Sĩ Lang Thang</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Nameless Knight</t>
+          <t>Hiệp Sĩ Vô Danh</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Waiter</t>
+          <t>Nhân viên phục vụ</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Commis Chef</t>
+          <t>Đầu Bếp Tập Sự</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Chef</t>
+          <t>Đầu Bếp</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Simulation Training</t>
+          <t>Huấn Luyện Mô Phỏng</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Simulation Training</t>
+          <t>Huấn Luyện Mô Phỏng</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Ray Tracing</t>
+          <t>Dò tia</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Ray-Traced Reflections</t>
+          <t>Phản chiếu bằng Dò tia</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Ray-Traced Global Illumination</t>
+          <t>Chiếu sáng toàn cầu bằng Dò tia</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Ray-Traced Shadows</t>
+          <t>Bóng đổ bằng Dò tia</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Co-op Teammate VFX</t>
+          <t>Hiệu Ứng Đồng Đội Hợp Tác</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Wounded Effect</t>
+          <t>Hiệu Ứng Bị Thương</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Frame Generation</t>
+          <t>Tạo Khung Hình</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Saturation</t>
+          <t>Bão Hòa</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Contrast</t>
+          <t>Tương Phản</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Furious Impact</t>
+          <t>Cú Đánh Cuồng Nộ</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Furious Surge</t>
+          <t>Sóng Cuồng Nộ</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Crescendo Impact</t>
+          <t>Va Chạm Cao Trào</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Dung Hợp Cộng Hưởng</t>
+          <t>Hợp Nhất Cộng Hưởng</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Wind Surge</t>
+          <t>Bùng Nổ Gió</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Sweeping Gale</t>
+          <t>Cơn Gió Quét</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Starfire Might</t>
+          <t>Sức Mạnh Sao Lửa</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Blazing Overdrive</t>
+          <t>Bùng Nổ Rực Lửa</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Overlapping Force</t>
+          <t>Lực Chồng Chất</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Singularity Reflection</t>
+          <t>Phản Chiếu Kỳ Dị</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Overlapping Force</t>
+          <t>Lực Chồng Chất</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Blazing Overdrive</t>
+          <t>Bùng Nổ Rực Lửa</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Overlapping Force</t>
+          <t>Lực Chồng Chất</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Flaming Zeal</t>
+          <t>Nhiệt Huyết Bừng Cháy</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Overlapping Force</t>
+          <t>Lực Chồng Chất</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Razorwind Rush</t>
+          <t>Đột Kích Razor Gió</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Overlapping Force</t>
+          <t>Lực Chồng Chất</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Avalanche Cascade</t>
+          <t>Thác Bão Tuyết</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Resonator Trang phục</t>
+          <t>Trang phục Resonator</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Hoa Đào</t>
+          <t>Hoa đào</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Lời nguyền Trừ tà</t>
+          <t>Lời Nguyền Trừ Tà</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Nữ Thần Nguyệt Quế</t>
+          <t>Nữ Thần Laurel</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Mùa Hè Rực Rỡ</t>
+          <t>Mùa Hè Bắn Tung Tóe</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>A Winged Song</t>
+          <t>Khúc Ca Cánh Chim</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>A Moment's Thông báo</t>
+          <t>Trong Chớp Mắt</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Lửa Hoang</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Budding Green</t>
+          <t>Mầm Xanh Mới Nhú</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Wandering Traveler</t>
+          <t>Lữ Khách Lang Thang</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Asura's Struggle</t>
+          <t>Cuộc Đấu Tranh Của Asura</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>A Quiet Moment</t>
+          <t>Khoảnh Khắc Yên Lặng</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Wandering Traveler</t>
+          <t>Lữ Khách Lang Thang</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Blooming Glory</t>
+          <t>Vinh Quang Nở Rộ</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Wooly Captain</t>
+          <t>Đội Trưởng Wooly</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Red Jade</t>
+          <t>Ngọc Bích Đỏ</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Information Broker</t>
+          <t>Người môi giới thông tin</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Heavy is the Burden</t>
+          <t>Gánh Nặng Nặng Trĩu</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Fiery Grace</t>
+          <t>Duyên Dáng Rực Rỡ</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>In Full Bloom</t>
+          <t>Trong Thời Khắc Nở Rộ</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>In the Shadows</t>
+          <t>Trong Bóng Tối</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Phantasmal Thread</t>
+          <t>Sợi Ảo Ảnh</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Dancing Lion's Blessing</t>
+          <t>Phước lành của Sư tử nhảy múa</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>An Elegant Cut</t>
+          <t>Phát Cắt Thanh Nhã</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Wandering Traveler</t>
+          <t>Lữ Khách Lang Thang</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Wandering Traveler</t>
+          <t>Lữ Khách Lang Thang</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Wandering Traveler</t>
+          <t>Lữ Khách Lang Thang</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>One with Everything</t>
+          <t>Hòa Nhập Vạn Vật</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Abyssal Ascension</t>
+          <t>Thăng Hoa Vực Sâu</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Resilient Truthseeker</t>
+          <t>Kẻ Tìm Kiếm Chân Lý Kiên Cường</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Light Lửa Than</t>
+          <t>Ánh Lửa Thiêng</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Mountain's Palette</t>
+          <t>Bảng Màu Núi Rừng</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>A Pure Heart</t>
+          <t>Một Trái Tim Trong Sáng</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Always and Ever</t>
+          <t>Mãi Mãi Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Wilderness Navigator</t>
+          <t>Hướng Đạo Viên Hoang Dã</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>What's in the Box</t>
+          <t>Có gì trong hộp vậy?</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Trendsetter</t>
+          <t>Người Định Hình Xu Hướng</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>The Sea's Act</t>
+          <t>Điệu Nhảy Của Đại Dương</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Hymn of the Deep</t>
+          <t>Khúc Ca Vực Sâu</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Wandering Traveler</t>
+          <t>Lữ Khách Lang Thang</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Hallucinative Hues</t>
+          <t>Sắc Màu Ảo Giác</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Songs of Seasons</t>
+          <t>Khúc Ca Bốn Mùa</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Daybreak Horizon</t>
+          <t>Chân Trời Bình Minh</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Thorny Rain</t>
+          <t>Mưa Gai</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Jinhsi – Premium Trang phục</t>
+          <t>Jinhsi – Trang phục Cao cấp</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Sanhua – Signature Trang phục</t>
+          <t>Sanhua – Trang phục đặc trưng</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Changli - Deluxe Trang phục</t>
+          <t>Changli - Trang phục Cao cấp</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Carlotta - Deluxe Trang phục</t>
+          <t>Carlotta - Trang phục Cao cấp</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Yangyang - Original Trang phục</t>
+          <t>Yangyang - Trang phục gốc</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Chixia - Original Trang phục</t>
+          <t>Chixia - Trang phục gốc</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Verina - Original Trang phục</t>
+          <t>Verina - Trang phục gốc</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Rover - Original Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục gốc</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Sanhua - Original Trang phục</t>
+          <t>Sanhua - Trang Phục Nguyên Bản</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Taoqi - Original Trang phục</t>
+          <t>Taoqi - Trang Phục Gốc</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Rover - Original Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục gốc</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Baizhi - Original Trang phục</t>
+          <t>Bạch Chi - Trang phục gốc</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Encore - Original Trang phục</t>
+          <t>Encore - Trang phục gốc</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Danjin - Original Trang phục</t>
+          <t>Danjin - Trang phục gốc</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Aalto - Original Trang phục</t>
+          <t>Aalto - Trang phục gốc</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Jiyan - Original Trang phục</t>
+          <t>Trang phục gốc của Jiyan</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Lupa - Original Trang phục</t>
+          <t>Lupa - Trang phục gốc</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Mortefi - Original Trang phục</t>
+          <t>Mortefi - Trang phục gốc</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Camellya - Original Trang phục</t>
+          <t>Camellya - Trang Phục Gốc</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Calcharo - Original Trang phục</t>
+          <t>Calcharo - Trang Phục Gốc</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Yinlin - Original Trang phục</t>
+          <t>Ân Lâm - Trang phục gốc</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Lingyang - Original Trang phục</t>
+          <t>Linh Dương - Trang phục gốc</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Yuanwu - Original Trang phục</t>
+          <t>Nguyên Vũ - Trang phục gốc</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Rover - Original Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục gốc</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Rover - Original Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục gốc</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Rover - Original Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục gốc</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Jianxin - Original Trang phục</t>
+          <t>Trang phục gốc của Jianxin</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Jinhsi - Original Trang phục</t>
+          <t>Kim Tư - Trang phục gốc</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Xiangli Yao - Original Trang phục</t>
+          <t>Xiangli Yao - Trang phục gốc</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Changli - Original Trang phục</t>
+          <t>Changli - Trang phục Nguyên bản</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Zhezhi - Original Trang phục</t>
+          <t>Triết Chi - Trang phục gốc</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Youhu - Original Trang phục</t>
+          <t>Youhu - Trang phục gốc</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Shorekeeper - Original Trang phục</t>
+          <t>Shorekeeper - Trang Phục Gốc</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Lumi - Original Trang phục</t>
+          <t>Lumi - Trang Phục Gốc</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Roccia - Original Trang phục</t>
+          <t>Trang phục gốc của Roccia</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Carlotta - Original Trang phục</t>
+          <t>Carlotta - Trang phục Nguyên bản</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Brant - Original Trang phục</t>
+          <t>Brant - Trang phục gốc</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Phoebe - Original Trang phục</t>
+          <t>Phoebe - Trang Phục Gốc</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Rover - Original Trang phục</t>
+          <t>Vận Mệnh Giả - Trang phục gốc</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Cantarella - Original Trang phục</t>
+          <t>Cantarella - Trang phục gốc</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Ciaccona - Original Trang phục</t>
+          <t>Ciaccona - Trang phục gốc</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Zani - Original Trang phục</t>
+          <t>Zani - Trang phục Nguyên bản</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Cartethyia - Original Trang phục</t>
+          <t>Cartethyia - Trang phục gốc</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>The Laureate</t>
+          <t>Nhà Vô Địch</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Honorary Aspect</t>
+          <t>Phẩm Chất Danh Dự</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Item dùng để thay đổi ngoại hình Echo Wings</t>
+          <t>Vật phẩm dùng để thay đổi ngoại hình Đôi Cánh Echo</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Clear Ngày</t>
+          <t>Hoàn Thành Ngày</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Exploration Aspect</t>
+          <t>Khía Cạnh Thám Hiểm</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Track Quest/Location</t>
+          <t>Theo dõi Nhiệm Vụ/Địa Điểm</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Nope</t>
+          <t>Không đời nào</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Annoyed</t>
+          <t>Bực mình</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Let's Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Oh Well...</t>
+          <t>Ôi trời...</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Tired</t>
+          <t>Mệt mỏi</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Chilling</t>
+          <t>Thư Giãn</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Smile</t>
+          <t>Nụ cười</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Gotcha</t>
+          <t>Bắt được rồi.</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Bất ngờ</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Wishing</t>
+          <t>Ước nguyện</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Đang làm việc</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Salute</t>
+          <t>Chào hỏi</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Ủa?</t>
+          <t>Ờ?</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Bài giảng</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Crestfallen</t>
+          <t>Thất Vọng</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Write a Letter</t>
+          <t>Viết một bức thư</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Ready? Go!</t>
+          <t>Sẵn sàng chưa? Bắt đầu!</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Clang Bang Hi</t>
+          <t>Ầm Dội xin chào</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Fired Up</t>
+          <t>Bừng Cháy</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Hug</t>
+          <t>Ôm</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Đã thất bại</t>
+          <t>Đã đánh bại</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Run!</t>
+          <t>Chạy đi!</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Bouncy</t>
+          <t>Nảy</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Curled Up</t>
+          <t>Thu mình lại</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Shocked</t>
+          <t>Bị sốc điện</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Take My Leave</t>
+          <t>Tôi xin phép cáo lui</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Whiff Whaff Hi</t>
+          <t>Phì Phò Chào</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Snip Snap Hi</t>
+          <t>Cắt Xén Hi</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Zig Zag Hi</t>
+          <t>Zig Zag Cao</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Tick Tack Hi</t>
+          <t>Tíc Tắc Xin Chào</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Shocked</t>
+          <t>Bị sốc điện</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Hungry</t>
+          <t>Đói quá...</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Delicious</t>
+          <t>Ngon tuyệt</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tummy Full</t>
+          <t>Bụng No</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Hello!</t>
+          <t>Chào cậu!</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Hear Không Evil</t>
+          <t>Không nghe điều ác</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Eavesdropping</t>
+          <t>Nghe lén à?</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Awkward</t>
+          <t>Ngại quá...</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Ehehe!</t>
+          <t>Hihi!</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Pass Out</t>
+          <t>Ngất xỉu</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Sleepy</t>
+          <t>Buồn ngủ</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Awake</t>
+          <t>Thức tỉnh</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Kudos</t>
+          <t>Tuyệt lắm</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Boo-hoo</t>
+          <t>Hu hu...</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Hmph!</t>
+          <t>Hừ!</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Cheers</t>
+          <t>Hoan hô!</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Phantom: Diggy Duggy</t>
+          <t>Bóng Ma: Đào Bới</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Phantom: Vitreum Dancer</t>
+          <t>Phantom: Vũ Công Pha Lê</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Phantom: Questless Knight</t>
+          <t>Hồn Ma: Kỵ Sĩ Vô Mục</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Phantom: Sentry Construct</t>
+          <t>Hồn Ma: Cấu Trúc Canh Gác</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Phantom: Lorelei</t>
+          <t>Hồn Ma: Lorelei</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Vui lòng đến Huanglong để tiếp tục</t>
+          <t>Hãy đến Huanglong để tiếp tục.</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Chọn một quân cờ hoặc vị trí</t>
+          <t>Chọn một mảnh ghép hoặc vị trí</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Like</t>
+          <t>Giống như</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Send Flowers</t>
+          <t>Gửi Hoa</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Wish</t>
+          <t>Ước Nguyện</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Cheer</t>
+          <t>Cổ vũ nào!</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Headpat</t>
+          <t>Xoa đầu</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Stretch</t>
+          <t>Duỗi người</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Giận dữ</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Bow</t>
+          <t>Cúi chào</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Sob</t>
+          <t>Hức...</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Cuddle</t>
+          <t>Ôm Ấm</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Pat</t>
+          <t>Vỗ</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Nhìn chằm chằm</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Peekaboo</t>
+          <t>Ú òa!</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Panic</t>
+          <t>Hoảng Loạn</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Upsy-daisy</t>
+          <t>Nhấc Lên Nào</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Frontier of Ruin</t>
+          <t>Biên giới hoang tàn</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Temporal Maze</t>
+          <t>Mê Cung Thời Gian</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Hidden Chamber</t>
+          <t>Phòng Ẩn</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Flowers of Oblivion</t>
+          <t>Hoa Lãng Quên</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Night's Aftersound</t>
+          <t>Dư Âm Của Đêm</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Birth of Darkness</t>
+          <t>Sự Ra Đời Của Bóng Tối</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Hiện tại bạn không thể sử dụng chức năng này</t>
+          <t>Hiện tại bạn không thể sử dụng chức năng này.</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Baiting</t>
+          <t>Dụ dỗ</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Di Chuyển Nhanh Đến Dock</t>
+          <t>Dịch chuyển Nhanh đến Bến tàu</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Nautical Light</t>
+          <t>Ánh Sáng Hàng Hải</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Sweet Puff</t>
+          <t>Bánh Ngọt Phồng</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Giữ&lt;/color&gt; mẻ câu của bạn và dùng gậy để kéo</t>
+          <t>Giữ &lt;color=Highlight&gt;con mồi&lt;/color&gt; và dùng cần câu để kéo nó về.</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Chạm&lt;/color&gt; vào mẻ câu để di chuyển sang phải</t>
+          <t>&lt;color=Highlight&gt;Chạm&lt;/color&gt; để bắt và di chuyển sang phải</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Quick Điều chỉnh</t>
+          <t>Điều chỉnh nhanh</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Switch Đội</t>
+          <t>Đổi Đội</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Đánh Giá</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Chọn Text</t>
+          <t>Chọn Văn Bản</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Move</t>
+          <t>Di Chuyển</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Color Settings</t>
+          <t>Cài Đặt Màu Sắc</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Sustain Sprint</t>
+          <t>Chạy Nước Rút Duy Trì</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Claimable</t>
+          <t>Có thể nhận</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Chọn Direction</t>
+          <t>Chọn Hướng</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Bearer of Legend</t>
+          <t>Người Mang Huyền Thoại</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Augusta - Original Trang phục</t>
+          <t>Augusta - Trang phục gốc</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>The Unmeasured One</t>
+          <t>Kẻ Không Đo Lường Được</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Iuno - Original Trang phục</t>
+          <t>Iuno - Trang phục gốc</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Auto Sprint</t>
+          <t>Tự Động Chạy</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Xem điều khoản</t>
+          <t>Xem thuật ngữ</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Double click to move</t>
+          <t>Nhấn đúp để di chuyển</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Điều chỉnh Map View</t>
+          <t>Điều chỉnh góc nhìn bản đồ</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Điều chỉnh View</t>
+          <t>Điều chỉnh góc nhìn</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Download Resources</t>
+          <t>Tải Xuống Tài Nguyên</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Combo!!</t>
+          <t>Hồi Chiêu!!</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Interactive Environment</t>
+          <t>Môi trường tương tác</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Show Username in Co-op</t>
+          <t>Hiển thị Tên Người Chơi trong Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Ineffective Area</t>
+          <t>Khu Vực Vô Hiệu</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Movement blocked</t>
+          <t>Di chuyển bị chặn</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Something is blocking your movement</t>
+          <t>Có gì đó đang chặn đường di chuyển của cậu.</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Chưa đủ điều kiện nhận thưởng</t>
+          <t>Chưa đủ điều kiện nhận phần thưởng</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Chưa đủ điều kiện nhận thưởng</t>
+          <t>Chưa đủ điều kiện nhận phần thưởng</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Đã nhận thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Chưa đủ điều kiện nhận thưởng</t>
+          <t>Chưa đủ điều kiện nhận phần thưởng</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Không data on file</t>
+          <t>Không có dữ liệu trong hồ sơ</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Max failed battle attempts reached</t>
+          <t>Đã đạt số lần thất bại tối đa trong trận chiến</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>This Resonator's level is maxed</t>
+          <t>Resonator này đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Preceding stage not cleared</t>
+          <t>Giai đoạn trước chưa hoàn thành</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Idle Animation: IV</t>
+          <t>Động tác chờ: IV</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Not yet at set birthday</t>
+          <t>Chưa đến ngày sinh đã cài đặt</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Resonator does not exist</t>
+          <t>Resonator không tồn tại</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Vui lòng thiết lập ngày sinh để mở khóa Birthday Wishes</t>
+          <t>Hãy đặt ngày sinh của bạn để mở khóa Lời Chúc Sinh Nhật.</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Bạn đã nhận Birthday Wishes cho năm nay</t>
+          <t>Bạn đã thu thập đủ Lời Chúc Sinh Nhật cho năm nay rồi</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Birthday Wishes sẽ được gửi qua thư trong game</t>
+          <t>Lời chúc sinh nhật sẽ được gửi qua thư trong game</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Ngày sinh phải được đặt lại trong năm hiện tại</t>
+          <t>Ngày sinh phải nằm trong năm hiện tại</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Birthday feature unavailable</t>
+          <t>Tính năng ngày sinh chưa khả dụng</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Vui lòng nhận quà sinh nhật trước</t>
+          <t>Hãy nhận quà sinh nhật trước đã.</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Resonator already invited</t>
+          <t>Resonator đã được mời</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Interact</t>
+          <t>Tương Tác</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>This module has been equipped</t>
+          <t>Đã trang bị mô-đun này</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Dawn upon Thorns</t>
+          <t>Bình Minh Giữa Gai Nhọn</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Premium Aspect</t>
+          <t>Thuộc Tính Cao Cấp</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Dawn upon Thorns</t>
+          <t>Bình Minh Giữa Gai Nhọn</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Premium Aspect</t>
+          <t>Thuộc Tính Cao Cấp</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Moment of Triumph</t>
+          <t>Khoảnh Khắc Chiến Thắng</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Exploration Aspect</t>
+          <t>Khía Cạnh Thám Hiểm</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Buffss</t>
+          <t>Buff</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>From the Beyond</t>
+          <t>Từ Thế Giới Bên Kia</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Phrolova - Original Trang phục</t>
+          <t>Phrolova - Trang phục gốc</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Phantasma Dreamland</t>
+          <t>Vùng Đất Mộng Ảo</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Rotate</t>
+          <t>Xoay</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Hồi tưởng</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Chế độ護 mắt</t>
+          <t>Chế Độ Chăm Sóc Mắt</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Chọn Chế độ</t>
+          <t>Chọn chế độ</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Color Temperature</t>
+          <t>Nhiệt Độ Màu</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Intensity</t>
+          <t>Cường độ</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Brightness</t>
+          <t>Ánh Sáng</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Texture Intensity</t>
+          <t>Cường độ Texture</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Foliage Density</t>
+          <t>Mật Độ Lá</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Switch Teams</t>
+          <t>Đổi Đội Hình</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Foliage Fade-Out</t>
+          <t>Lá Tan Biến</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Intel Intel XeSS2</t>
+          <t>XeSS2</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
